--- a/travel_log_template.xlsx
+++ b/travel_log_template.xlsx
@@ -425,12 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,10 +442,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>End Date</t>
         </is>
@@ -458,27 +464,59 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2024-06-14</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>2024-06-15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2024-06-22</t>
         </is>
@@ -486,7 +524,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:C202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="Travel log" prompt="Dates must be YYYY-MM-DD. Ranges should not overlap." type="textLength" operator="greaterThan">
+    <dataValidation sqref="A2:D203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" promptTitle="Travel log" prompt="Place is optional. Dates must be YYYY-MM-DD. Don't let two places share a day: end one stay the day before the next starts." type="textLength" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
